--- a/inputs/input.xlsx
+++ b/inputs/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Profesh\Forward Edge AI\Treasury AI\single-finding-fix\mdl-backend-demo\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691519CF-F542-47CC-8821-2A1C38827AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE2D654-7DD4-4AD0-86AB-4AD6EDA7149C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32505" yWindow="4500" windowWidth="19365" windowHeight="10035" xr2:uid="{72F4E804-3F27-4A25-B0E1-689D681CEDC7}"/>
+    <workbookView xWindow="28695" yWindow="1545" windowWidth="23175" windowHeight="14055" xr2:uid="{72F4E804-3F27-4A25-B0E1-689D681CEDC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>EIN</t>
   </si>
@@ -81,6 +81,39 @@
   </si>
   <si>
     <t> 04-6001109 </t>
+  </si>
+  <si>
+    <t>Auditee_name</t>
+  </si>
+  <si>
+    <t>City Of Decatur</t>
+  </si>
+  <si>
+    <t>City of New London</t>
+  </si>
+  <si>
+    <t>City of Webster Groves</t>
+  </si>
+  <si>
+    <t>County of Mariposa</t>
+  </si>
+  <si>
+    <t>County of Washington New York</t>
+  </si>
+  <si>
+    <t>Gallatin County</t>
+  </si>
+  <si>
+    <t>Presidio County</t>
+  </si>
+  <si>
+    <t>Town of Blacksburg Virginia</t>
+  </si>
+  <si>
+    <t>Town of Charlton</t>
+  </si>
+  <si>
+    <t>City of Oregon</t>
   </si>
 </sst>
 </file>
@@ -496,98 +529,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CE356D-F547-4C03-B419-CF0B195CD08D}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>2023</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="2">
         <v>2024</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
